--- a/rules/CORE-000746/positive/01/data/unit-test-coreid-FB5801-positive_01.xlsx
+++ b/rules/CORE-000746/positive/01/data/unit-test-coreid-FB5801-positive_01.xlsx
@@ -1363,7 +1363,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>CDISC-TEST</t>
+          <t>CDISCCORE01</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>CDISC-TEST</t>
+          <t>CDISCCORE01</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
